--- a/semester 2/BI/BBCA.JK_2021-01-01_2025-12-31.xlsx
+++ b/semester 2/BI/BBCA.JK_2021-01-01_2025-12-31.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DATA ARSIP\IJAZAH KOMPUTERKU\THESIS\semester 2\BI\DATA SAHAM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adi\Documents\GitHub\thesiss2\semester 2\BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F7B78C-6ACE-4CDE-BC0A-F61CA493B63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -145,7 +145,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -254,7 +254,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -264,15 +264,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -284,6 +275,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,28 +473,28 @@
       <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="8">
         <v>2021</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="8">
         <v>2022</v>
       </c>
     </row>
@@ -524,7 +524,7 @@
         <f>IF(F3&gt;F2,"Naik",IF(F3&lt;F2,"Turun","Stabil"))</f>
         <v>Naik</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="12">
         <v>2021</v>
       </c>
       <c r="K3" s="6" t="s">
@@ -542,7 +542,7 @@
         <f>COUNTIF(jan_21,"Stabil")</f>
         <v>1</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="Q3" s="7" t="s">
@@ -578,7 +578,7 @@
         <f t="shared" ref="H4:H73" si="0">IF(F4&gt;F3,"Naik",IF(F4&lt;F3,"Turun","Stabil"))</f>
         <v>Turun</v>
       </c>
-      <c r="J4" s="9"/>
+      <c r="J4" s="13"/>
       <c r="K4" s="6" t="s">
         <v>14</v>
       </c>
@@ -594,7 +594,7 @@
         <f>COUNTIF(feb_21,"Stabil")</f>
         <v>0</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="P4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="Q4" s="7" t="s">
@@ -630,7 +630,7 @@
         <f t="shared" si="0"/>
         <v>Naik</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="6" t="s">
         <v>15</v>
       </c>
@@ -646,7 +646,7 @@
         <f>COUNTIF(mar_21,"Stabil")</f>
         <v>0</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="9" t="s">
         <v>15</v>
       </c>
       <c r="Q5" s="7" t="s">
@@ -682,7 +682,7 @@
         <f t="shared" si="0"/>
         <v>Naik</v>
       </c>
-      <c r="J6" s="9"/>
+      <c r="J6" s="13"/>
       <c r="K6" s="6" t="s">
         <v>16</v>
       </c>
@@ -698,7 +698,7 @@
         <f>COUNTIF(apr_21,"Stabil")</f>
         <v>0</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="P6" s="9" t="s">
         <v>16</v>
       </c>
       <c r="Q6" s="7" t="s">
@@ -734,7 +734,7 @@
         <f t="shared" si="0"/>
         <v>Naik</v>
       </c>
-      <c r="J7" s="9"/>
+      <c r="J7" s="13"/>
       <c r="K7" s="6" t="s">
         <v>17</v>
       </c>
@@ -750,13 +750,13 @@
         <f>COUNTIF(mei_21,"Stabil")</f>
         <v>1</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="P7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="13"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -784,7 +784,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J8" s="9"/>
+      <c r="J8" s="13"/>
       <c r="K8" s="6" t="s">
         <v>18</v>
       </c>
@@ -800,7 +800,7 @@
         <f>COUNTIF(jun_21,"Stabil")</f>
         <v>0</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="P8" s="9" t="s">
         <v>18</v>
       </c>
       <c r="Q8" s="7" t="s">
@@ -836,7 +836,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J9" s="9"/>
+      <c r="J9" s="13"/>
       <c r="K9" s="6" t="s">
         <v>19</v>
       </c>
@@ -852,7 +852,7 @@
         <f>COUNTIF(jul_21,"Stabil")</f>
         <v>2</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="P9" s="9" t="s">
         <v>19</v>
       </c>
       <c r="Q9" s="7" t="s">
@@ -888,7 +888,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J10" s="9"/>
+      <c r="J10" s="13"/>
       <c r="K10" s="6" t="s">
         <v>20</v>
       </c>
@@ -904,7 +904,7 @@
         <f>COUNTIF(agu_21,"Stabil")</f>
         <v>4</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="9" t="s">
         <v>20</v>
       </c>
       <c r="Q10" s="7" t="s">
@@ -940,7 +940,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J11" s="9"/>
+      <c r="J11" s="13"/>
       <c r="K11" s="6" t="s">
         <v>21</v>
       </c>
@@ -956,7 +956,7 @@
         <f>COUNTIF(sep_21,"Stabil")</f>
         <v>0</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="P11" s="9" t="s">
         <v>21</v>
       </c>
       <c r="Q11" s="7" t="s">
@@ -992,7 +992,7 @@
         <f t="shared" si="0"/>
         <v>Naik</v>
       </c>
-      <c r="J12" s="9"/>
+      <c r="J12" s="13"/>
       <c r="K12" s="6" t="s">
         <v>22</v>
       </c>
@@ -1008,13 +1008,13 @@
         <f>COUNTIF(okt_21,"Stabil")</f>
         <v>2</v>
       </c>
-      <c r="P12" s="12" t="s">
+      <c r="P12" s="9" t="s">
         <v>22</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="R12" s="13"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -1042,26 +1042,26 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="14" t="s">
+      <c r="J13" s="13"/>
+      <c r="K13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="11">
         <f>COUNTIF(nov_21,"Naik")</f>
         <v>10</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="11">
         <f>COUNTIF(nov_21,"Turun")</f>
         <v>10</v>
       </c>
-      <c r="N13" s="14">
+      <c r="N13" s="11">
         <f>COUNTIF(nov_21,"Stabil")</f>
         <v>2</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="P13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q13" s="13"/>
+      <c r="Q13" s="10"/>
       <c r="R13" s="7" t="s">
         <v>9</v>
       </c>
@@ -1092,7 +1092,7 @@
         <f t="shared" si="0"/>
         <v>Stabil</v>
       </c>
-      <c r="J14" s="10"/>
+      <c r="J14" s="14"/>
       <c r="K14" s="6" t="s">
         <v>24</v>
       </c>
@@ -1108,7 +1108,7 @@
         <f>COUNTIF(des_21,"Stabil")</f>
         <v>7</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="P14" s="9" t="s">
         <v>24</v>
       </c>
       <c r="Q14" s="7" t="s">
@@ -1144,7 +1144,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="12">
         <v>2022</v>
       </c>
       <c r="K15" s="6" t="s">
@@ -1189,7 +1189,7 @@
         <f t="shared" si="0"/>
         <v>Naik</v>
       </c>
-      <c r="J16" s="9"/>
+      <c r="J16" s="13"/>
       <c r="K16" s="6" t="s">
         <v>14</v>
       </c>
@@ -1232,7 +1232,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J17" s="9"/>
+      <c r="J17" s="13"/>
       <c r="K17" s="6" t="s">
         <v>15</v>
       </c>
@@ -1275,7 +1275,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J18" s="9"/>
+      <c r="J18" s="13"/>
       <c r="K18" s="6" t="s">
         <v>16</v>
       </c>
@@ -1318,19 +1318,19 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="14" t="s">
+      <c r="J19" s="13"/>
+      <c r="K19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="11">
         <f>COUNTIF(mei_22,"Naik")</f>
         <v>7</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="11">
         <f>COUNTIF(mei_22,"Turun")</f>
         <v>7</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="11">
         <f>COUNTIF(mei_22,"Stabil")</f>
         <v>1</v>
       </c>
@@ -1361,7 +1361,7 @@
         <f t="shared" si="0"/>
         <v>Naik</v>
       </c>
-      <c r="J20" s="9"/>
+      <c r="J20" s="13"/>
       <c r="K20" s="6" t="s">
         <v>18</v>
       </c>
@@ -1404,7 +1404,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J21" s="9"/>
+      <c r="J21" s="13"/>
       <c r="K21" s="6" t="s">
         <v>19</v>
       </c>
@@ -1427,7 +1427,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="J22" s="9"/>
+      <c r="J22" s="13"/>
       <c r="K22" s="6" t="s">
         <v>20</v>
       </c>
@@ -1450,7 +1450,7 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="J23" s="9"/>
+      <c r="J23" s="13"/>
       <c r="K23" s="6" t="s">
         <v>21</v>
       </c>
@@ -1493,19 +1493,19 @@
         <f>IF(F24&gt;F21,"Naik",IF(F24&lt;F21,"Turun","Stabil"))</f>
         <v>Naik</v>
       </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="14" t="s">
+      <c r="J24" s="13"/>
+      <c r="K24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="11">
         <f>COUNTIF(okt_22,"Naik")</f>
         <v>10</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M24" s="11">
         <f>COUNTIF(okt_22,"Turun")</f>
         <v>10</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24" s="11">
         <f>COUNTIF(okt_22,"Stabil")</f>
         <v>1</v>
       </c>
@@ -1536,7 +1536,7 @@
         <f t="shared" si="0"/>
         <v>Turun</v>
       </c>
-      <c r="J25" s="9"/>
+      <c r="J25" s="13"/>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
@@ -1579,7 +1579,7 @@
         <f t="shared" si="0"/>
         <v>Naik</v>
       </c>
-      <c r="J26" s="10"/>
+      <c r="J26" s="14"/>
       <c r="K26" s="6" t="s">
         <v>24</v>
       </c>
